--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N77_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N77_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>86.3898013871698</v>
+        <v>14.03834272541509</v>
       </c>
       <c r="D2" t="n">
-        <v>33.19390211689795</v>
+        <v>5.394009093995916</v>
       </c>
       <c r="E2" t="n">
-        <v>18.02992939128069</v>
+        <v>2.929863526083112</v>
       </c>
       <c r="F2" t="n">
-        <v>12.57602031696307</v>
+        <v>2.043603301506498</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.34151566224845</v>
+        <v>5.255496295115373</v>
       </c>
       <c r="D3" t="n">
-        <v>32.5115377781496</v>
+        <v>5.283124888949311</v>
       </c>
       <c r="E3" t="n">
-        <v>18.02992939128069</v>
+        <v>2.929863526083112</v>
       </c>
       <c r="F3" t="n">
-        <v>12.57602031696307</v>
+        <v>2.043603301506498</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>23.73988509080432</v>
+        <v>3.857731327255702</v>
       </c>
       <c r="D4" t="n">
-        <v>23.91508492664805</v>
+        <v>3.886201300580309</v>
       </c>
       <c r="E4" t="n">
-        <v>18.02992939128069</v>
+        <v>2.929863526083112</v>
       </c>
       <c r="F4" t="n">
-        <v>12.57602031696307</v>
+        <v>2.043603301506498</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>18.41166288995043</v>
+        <v>2.991895219616945</v>
       </c>
       <c r="D5" t="n">
-        <v>18.57599885098208</v>
+        <v>3.018599813284588</v>
       </c>
       <c r="E5" t="n">
-        <v>18.02992939128069</v>
+        <v>2.929863526083112</v>
       </c>
       <c r="F5" t="n">
-        <v>12.57602031696307</v>
+        <v>2.043603301506498</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.63556366284374</v>
+        <v>5.628279095212108</v>
       </c>
       <c r="D6" t="n">
-        <v>34.73396722559213</v>
+        <v>5.644269674158721</v>
       </c>
       <c r="E6" t="n">
-        <v>18.02992939128069</v>
+        <v>2.929863526083112</v>
       </c>
       <c r="F6" t="n">
-        <v>12.57602031696307</v>
+        <v>2.043603301506498</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>61.29631646427642</v>
+        <v>9.960651425444917</v>
       </c>
       <c r="D7" t="n">
-        <v>30.48746481315711</v>
+        <v>4.95421303213803</v>
       </c>
       <c r="E7" t="n">
-        <v>18.02992939128069</v>
+        <v>2.929863526083112</v>
       </c>
       <c r="F7" t="n">
-        <v>12.57602031696307</v>
+        <v>2.043603301506498</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>54.99278605452894</v>
+        <v>8.936327733860953</v>
       </c>
       <c r="D8" t="n">
-        <v>36.5173403570444</v>
+        <v>5.934067808019715</v>
       </c>
       <c r="E8" t="n">
-        <v>18.02992939128069</v>
+        <v>2.929863526083112</v>
       </c>
       <c r="F8" t="n">
-        <v>12.57602031696307</v>
+        <v>2.043603301506498</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>20.44557518566894</v>
+        <v>3.322405967671202</v>
       </c>
       <c r="D9" t="n">
-        <v>20.48608924113523</v>
+        <v>3.328989501684475</v>
       </c>
       <c r="E9" t="n">
-        <v>18.02992939128069</v>
+        <v>2.929863526083112</v>
       </c>
       <c r="F9" t="n">
-        <v>12.57602031696307</v>
+        <v>2.043603301506498</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>16.3511601217625</v>
+        <v>2.657063519786406</v>
       </c>
       <c r="D10" t="n">
-        <v>16.45423872193846</v>
+        <v>2.673813792314999</v>
       </c>
       <c r="E10" t="n">
-        <v>18.02992939128069</v>
+        <v>2.929863526083112</v>
       </c>
       <c r="F10" t="n">
-        <v>12.57602031696307</v>
+        <v>2.043603301506498</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>14.03730262127501</v>
+        <v>2.28106167595719</v>
       </c>
       <c r="D11" t="n">
-        <v>13.97774994957823</v>
+        <v>2.271384366806462</v>
       </c>
       <c r="E11" t="n">
-        <v>18.02992939128069</v>
+        <v>2.929863526083112</v>
       </c>
       <c r="F11" t="n">
-        <v>12.57602031696307</v>
+        <v>2.043603301506498</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>33.9726895680912</v>
+        <v>5.52056205481482</v>
       </c>
       <c r="D12" t="n">
-        <v>33.97380740375055</v>
+        <v>5.520743703109464</v>
       </c>
       <c r="E12" t="n">
-        <v>18.02992939128069</v>
+        <v>2.929863526083112</v>
       </c>
       <c r="F12" t="n">
-        <v>12.57602031696307</v>
+        <v>2.043603301506498</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>15.92957278244648</v>
+        <v>2.588555577147553</v>
       </c>
       <c r="D13" t="n">
-        <v>15.79134816971421</v>
+        <v>2.566094077578559</v>
       </c>
       <c r="E13" t="n">
-        <v>18.02992939128069</v>
+        <v>2.929863526083112</v>
       </c>
       <c r="F13" t="n">
-        <v>12.57602031696307</v>
+        <v>2.043603301506498</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>29.08813019358508</v>
+        <v>4.726821156457576</v>
       </c>
       <c r="D14" t="n">
-        <v>16.39098254012366</v>
+        <v>2.663534662770095</v>
       </c>
       <c r="E14" t="n">
-        <v>18.02992939128069</v>
+        <v>2.929863526083112</v>
       </c>
       <c r="F14" t="n">
-        <v>12.57602031696307</v>
+        <v>2.043603301506498</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>61.94932614709159</v>
+        <v>10.06676549890238</v>
       </c>
       <c r="D15" t="n">
-        <v>17.19117672934432</v>
+        <v>2.793566218518452</v>
       </c>
       <c r="E15" t="n">
-        <v>18.02992939128069</v>
+        <v>2.929863526083112</v>
       </c>
       <c r="F15" t="n">
-        <v>12.57602031696307</v>
+        <v>2.043603301506498</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>38.83168203552643</v>
+        <v>6.310148330773044</v>
       </c>
       <c r="D16" t="n">
-        <v>37.76084730704286</v>
+        <v>6.136137687394465</v>
       </c>
       <c r="E16" t="n">
-        <v>18.02992939128069</v>
+        <v>2.929863526083112</v>
       </c>
       <c r="F16" t="n">
-        <v>12.57602031696307</v>
+        <v>2.043603301506498</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>42.93518340132578</v>
+        <v>6.97696730271544</v>
       </c>
       <c r="D17" t="n">
-        <v>3.375763016153615</v>
+        <v>0.5485614901249625</v>
       </c>
       <c r="E17" t="n">
-        <v>18.02992939128069</v>
+        <v>2.929863526083112</v>
       </c>
       <c r="F17" t="n">
-        <v>12.57602031696307</v>
+        <v>2.043603301506498</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>30.27043164444454</v>
+        <v>4.918945142222237</v>
       </c>
       <c r="D18" t="n">
-        <v>29.07912706282837</v>
+        <v>4.72535814770961</v>
       </c>
       <c r="E18" t="n">
-        <v>18.02992939128069</v>
+        <v>2.929863526083112</v>
       </c>
       <c r="F18" t="n">
-        <v>12.57602031696307</v>
+        <v>2.043603301506498</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>27.74432146952346</v>
+        <v>4.508452238797562</v>
       </c>
       <c r="D19" t="n">
-        <v>26.59010304973941</v>
+        <v>4.320891745582655</v>
       </c>
       <c r="E19" t="n">
-        <v>18.02992939128069</v>
+        <v>2.929863526083112</v>
       </c>
       <c r="F19" t="n">
-        <v>12.57602031696307</v>
+        <v>2.043603301506498</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>45.08257800205043</v>
+        <v>7.325918925333196</v>
       </c>
       <c r="D20" t="n">
-        <v>12.09440216877289</v>
+        <v>1.965340352425594</v>
       </c>
       <c r="E20" t="n">
-        <v>18.02992939128069</v>
+        <v>2.929863526083112</v>
       </c>
       <c r="F20" t="n">
-        <v>12.57602031696307</v>
+        <v>2.043603301506498</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>36.94756826402359</v>
+        <v>6.003979842903834</v>
       </c>
       <c r="D21" t="n">
-        <v>20.13331372118797</v>
+        <v>3.271663479693045</v>
       </c>
       <c r="E21" t="n">
-        <v>18.02992939128069</v>
+        <v>2.929863526083112</v>
       </c>
       <c r="F21" t="n">
-        <v>12.57602031696307</v>
+        <v>2.043603301506498</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>45.45219920850575</v>
+        <v>7.385982371382185</v>
       </c>
       <c r="D22" t="n">
-        <v>27.90216031234545</v>
+        <v>4.534101050756135</v>
       </c>
       <c r="E22" t="n">
-        <v>18.02992939128069</v>
+        <v>2.929863526083112</v>
       </c>
       <c r="F22" t="n">
-        <v>12.57602031696307</v>
+        <v>2.043603301506498</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>13.14987553810453</v>
+        <v>2.136854774941987</v>
       </c>
       <c r="D23" t="n">
-        <v>12.09013885848114</v>
+        <v>1.964647564503185</v>
       </c>
       <c r="E23" t="n">
-        <v>18.02992939128069</v>
+        <v>2.929863526083112</v>
       </c>
       <c r="F23" t="n">
-        <v>12.57602031696307</v>
+        <v>2.043603301506498</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>70.57520275908126</v>
+        <v>11.46847044835071</v>
       </c>
       <c r="D24" t="n">
-        <v>44.39017478989877</v>
+        <v>7.213403403358551</v>
       </c>
       <c r="E24" t="n">
-        <v>18.02992939128069</v>
+        <v>2.929863526083112</v>
       </c>
       <c r="F24" t="n">
-        <v>12.57602031696307</v>
+        <v>2.043603301506498</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>14.20837254704717</v>
+        <v>2.308860538895165</v>
       </c>
       <c r="D25" t="n">
-        <v>13.30702381891143</v>
+        <v>2.162391370573107</v>
       </c>
       <c r="E25" t="n">
-        <v>18.02992939128069</v>
+        <v>2.929863526083112</v>
       </c>
       <c r="F25" t="n">
-        <v>12.57602031696307</v>
+        <v>2.043603301506498</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>30.03755928050005</v>
+        <v>4.881103383081259</v>
       </c>
       <c r="D26" t="n">
-        <v>30.08073574026028</v>
+        <v>4.888119557792296</v>
       </c>
       <c r="E26" t="n">
-        <v>18.02992939128069</v>
+        <v>2.929863526083112</v>
       </c>
       <c r="F26" t="n">
-        <v>12.57602031696307</v>
+        <v>2.043603301506498</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>51.91044193152251</v>
+        <v>8.435446813872408</v>
       </c>
       <c r="D27" t="n">
-        <v>43.97664616633433</v>
+        <v>7.146205002029328</v>
       </c>
       <c r="E27" t="n">
-        <v>18.02992939128069</v>
+        <v>2.929863526083112</v>
       </c>
       <c r="F27" t="n">
-        <v>12.57602031696307</v>
+        <v>2.043603301506498</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>24.62783920124317</v>
+        <v>4.002023870202015</v>
       </c>
       <c r="D28" t="n">
-        <v>25.67767061584252</v>
+        <v>4.172621475074409</v>
       </c>
       <c r="E28" t="n">
-        <v>18.02992939128069</v>
+        <v>2.929863526083112</v>
       </c>
       <c r="F28" t="n">
-        <v>12.57602031696307</v>
+        <v>2.043603301506498</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>42.31590106815204</v>
+        <v>6.876333923574706</v>
       </c>
       <c r="D29" t="n">
-        <v>42.85866311518051</v>
+        <v>6.964532756216833</v>
       </c>
       <c r="E29" t="n">
-        <v>18.02992939128069</v>
+        <v>2.929863526083112</v>
       </c>
       <c r="F29" t="n">
-        <v>12.57602031696307</v>
+        <v>2.043603301506498</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>60.79591377807471</v>
+        <v>9.879335988937139</v>
       </c>
       <c r="D30" t="n">
-        <v>47.22702052019303</v>
+        <v>7.674390834531367</v>
       </c>
       <c r="E30" t="n">
-        <v>18.02992939128069</v>
+        <v>2.929863526083112</v>
       </c>
       <c r="F30" t="n">
-        <v>12.57602031696307</v>
+        <v>2.043603301506498</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>59.32962518541993</v>
+        <v>9.641064092630739</v>
       </c>
       <c r="D31" t="n">
-        <v>54.59870687245988</v>
+        <v>8.872289866774731</v>
       </c>
       <c r="E31" t="n">
-        <v>18.02992939128069</v>
+        <v>2.929863526083112</v>
       </c>
       <c r="F31" t="n">
-        <v>12.57602031696307</v>
+        <v>2.043603301506498</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>39.36545172639081</v>
+        <v>6.396885905538507</v>
       </c>
       <c r="D32" t="n">
-        <v>40.2482009176918</v>
+        <v>6.540332649124918</v>
       </c>
       <c r="E32" t="n">
-        <v>18.02992939128069</v>
+        <v>2.929863526083112</v>
       </c>
       <c r="F32" t="n">
-        <v>12.57602031696307</v>
+        <v>2.043603301506498</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>49.07623408382926</v>
+        <v>7.974888038622255</v>
       </c>
       <c r="D33" t="n">
-        <v>50.22908154087472</v>
+        <v>8.162225750392142</v>
       </c>
       <c r="E33" t="n">
-        <v>18.02992939128069</v>
+        <v>2.929863526083112</v>
       </c>
       <c r="F33" t="n">
-        <v>12.57602031696307</v>
+        <v>2.043603301506498</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
